--- a/weight对比.xlsx
+++ b/weight对比.xlsx
@@ -4,28 +4,73 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="11531" windowHeight="8807"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+  <si>
+    <t>mask = - distance * a - size * b;</t>
+  </si>
+  <si>
+    <t>write_single_rep3</t>
+  </si>
+  <si>
+    <t>write_single_rep2</t>
+  </si>
+  <si>
+    <t>a(距离)</t>
+  </si>
+  <si>
+    <t>b(任务数)</t>
+  </si>
+  <si>
+    <t>得分</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -370,12 +415,147 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -496,138 +676,198 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,9 +1181,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.66666666666667" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
+    <col min="6" max="6" width="10.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="14.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="8.66666666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.7777777777778" customWidth="1"/>
+    <col min="11" max="11" width="14.1111111111111" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.35" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="17"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10">
+        <v>24908007.8348</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>25349088.5572</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="K4" s="13">
+        <v>26088291.4722</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>25359132.7973</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>25599509.5572</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8">
+        <v>0.28</v>
+      </c>
+      <c r="J5" s="9">
+        <f>1-I5</f>
+        <v>0.72</v>
+      </c>
+      <c r="K5" s="10">
+        <v>26321687.6373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="10">
+        <v>25332688.0373</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="10">
+        <v>25850010.0372</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="J6" s="9">
+        <f t="shared" ref="J6:J14" si="0">1-I6</f>
+        <v>0.74</v>
+      </c>
+      <c r="K6" s="10">
+        <v>26315278.8798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="10">
+        <v>25594939.2448</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="10">
+        <v>25730590.1447</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="J7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.76</v>
+      </c>
+      <c r="K7" s="10">
+        <v>26368722.2798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="10">
+        <v>25421260.2098</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="G8" s="10">
+        <v>25710883.8848</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="J8" s="9">
+        <f t="shared" si="0"/>
+        <v>0.78</v>
+      </c>
+      <c r="K8" s="13">
+        <v>26116287.7998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="10">
+        <v>25546954.7373</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>25980287.9922</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K9" s="13">
+        <v>26360306.9723</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="B10" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="13">
+        <v>25799004.8323</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="G10" s="13">
+        <v>25958022.2448</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="J10" s="9">
+        <f t="shared" si="0"/>
+        <v>0.82</v>
+      </c>
+      <c r="K10" s="13">
+        <v>26362024.3223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="C11" s="13">
+        <v>25995272.8723</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="G11" s="13">
+        <v>26088291.4722</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="J11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+      <c r="K11" s="13">
+        <v>26305103.6673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="B12" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="C12" s="13">
+        <v>26295549.7198</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="13">
+        <v>26360306.9723</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="11">
+        <v>0.14</v>
+      </c>
+      <c r="J12" s="9">
+        <f t="shared" si="0"/>
+        <v>0.86</v>
+      </c>
+      <c r="K12" s="13">
+        <v>26362617.1498</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="C13" s="13">
+        <v>26152782.3673</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="13">
+        <v>26043903.5498</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="0"/>
+        <v>0.88</v>
+      </c>
+      <c r="K13" s="13">
+        <v>26236137.5073</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" spans="1:11">
+      <c r="A14" s="14">
+        <v>0</v>
+      </c>
+      <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="C14" s="16">
+        <v>22314479.3374</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16">
+        <v>22695218.3248</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="K14" s="20">
+        <v>26043903.5498</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I2:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -954,7 +1628,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -966,7 +1640,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
